--- a/BOSMAX_PRODUCT_COPYWRITING_LIBRARY_v1.xlsx
+++ b/BOSMAX_PRODUCT_COPYWRITING_LIBRARY_v1.xlsx
@@ -107,7 +107,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,6 +118,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -153,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -161,11 +166,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -183,6 +194,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1583,7 +1597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2171,396 @@
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>Representative Fastmoss starter row. Generalize before large-scale Antigravity fill if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BEAUTY_CONFIDENCE_R004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BEAUTY_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Beauty Confidence Direct</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Skincare / Cosmetics</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Beauty Product</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>beauty_confidence_direct</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_ANG_004</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Skin barrier recovery</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_HOOK_004</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Muka kering dan kusam? Pulihkan pelindung kulit semulajadi dalam 7 hari.</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Formula asid hyaluronic pekat menghidrasi kulit mendalam.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Bebas alkohol dan paraben, selamat untuk kulit sensitif.</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Mengunci kelembapan kulit untuk menghalang kerosakan luar.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_CTA_004</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>Kembalikan kulit sihat berseri anda sekarang.</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>Generic Beauty Confidence row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BEAUTY_CONFIDENCE_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BEAUTY_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Beauty Confidence Direct</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Skincare / Cosmetics</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Beauty Product</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>beauty_confidence_direct</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_ANG_005</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Instant makeup glow</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_HOOK_005</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Kulit nampak glowing dan berseri di bawah mekap tanpa rasa berminyak.</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Tekstur ringan cepat menyerap tanpa menyumbat pori.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Kemasan satin semula jadi membuat mekap kelihatan flawless.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Membantu mengekalkan mekap tahan lama sepanjang hari.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_CTA_005</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Dapatkan glow instant anda hari ini.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>HPAS</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Generic Beauty Confidence row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BEAUTY_CONFIDENCE_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BEAUTY_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Beauty Confidence Direct</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Skincare / Cosmetics</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Beauty Product</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>beauty_confidence_direct</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_ANG_006</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Natural skin compatibility</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_HOOK_006</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk semua jenis kulit termasuk yang paling sensitif.</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Bahan organik semulajadi diuji secara klinikal.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Bebas daripada 10 bahan kimia berbahaya.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Formula pH seimbang yang memelihara ekosistem kulit.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>BEAUTY_CTA_006</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Cuba hari ini tanpa ragu-ragu.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Generic Beauty Confidence row.</t>
         </is>
       </c>
     </row>
@@ -3983,7 +4387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -4557,6 +4961,396 @@
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>Representative Fastmoss starter row. Generalize before large-scale Antigravity fill if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BODY_CARE_FRESHNESS_R004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BODY_CARE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Body Care Freshness Direct</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Body Care / Personal Hygiene</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Body Wash / Deodorant</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>body_care_freshness_direct</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_ANG_004</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Clean hygiene &amp; cooling refreshener</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_HOOK_004</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Bau peluh selepas aktiviti luar hilang serta-merta dengan mandian herba.</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Formula antibakteria semula jadi yang mematikan kuman.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Aroma mentol sejuk melegakan badan yang lesu.</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Menghilangkan daki dan peluh degil dengan berkesan.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_CTA_004</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>Kekal bersih, wangi dan segar hari ini.</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>Generic Body Care Freshness row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BODY_CARE_FRESHNESS_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BODY_CARE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Body Care Freshness Direct</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Body Care / Personal Hygiene</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Body Wash / Deodorant</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>body_care_freshness_direct</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_ANG_005</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>24h active odor protection</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_HOOK_005</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Beli pelindung bau badan yang tahan 24 jam walaupun cuaca panas terik.</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Anti-odor aktif semulajadi menghalang pembiakan bakteria.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Tidak meninggalkan kesan kekuningan pada pakaian.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Memberikan perlindungan peluh berpanjangan.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_CTA_005</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Checkout sekarang untuk perlindungan penuh.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Generic Body Care Freshness row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BODY_CARE_FRESHNESS_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_BODY_CARE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Body Care Freshness Direct</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Body Care / Personal Hygiene</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Body Wash / Deodorant</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>body_care_freshness_direct</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_ANG_006</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Deep skin moisturization</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_HOOK_006</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Kulit kering bersisik kembali lembut dan licin selepas mandi.</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Kaya dengan vitamin E dan pati kelapa semulajadi.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Melembabkan kulit kering tanpa melekit.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Tekstur krim kaya buih yang memanjakan kulit.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>BODY_CARE_CTA_006</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Manjakan kulit anda dengan kesegaran sekarang.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>HPAS</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Generic Body Care Freshness row.</t>
         </is>
       </c>
     </row>
@@ -9574,7 +10368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10148,6 +10942,396 @@
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>Representative Fastmoss starter row. Generalize before large-scale Antigravity fill if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_MEN_PERFUME_R004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_MEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Men Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Men's Perfume</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>men_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_ANG_004</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Longevity &amp; Professional confidence</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_HOOK_004</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Bau wangi tahan 12 jam, meeting seharian pun tak hilang keyakinan.</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Formula Eau de Parfum (EDP) dengan kepekatan minyak wangian tinggi.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Profil bau maskulin profesional yang tenang dan meyakinkan.</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk kegunaan harian di tempat kerja berhawa dingin.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_CTA_004</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>Dapatkan wangian bertahan sepanjang hari anda.</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>Generic Men Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_MEN_PERFUME_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_MEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Men Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Men's Perfume</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>men_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_ANG_005</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Attraction &amp; Pheromone appeal</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_HOOK_005</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Bau yang buat pasangan terpikat dan selesa sepanjang malam.</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Profil bau premium dengan sentuhan pheromone maskulin.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Meningkatkan daya tarikan dan karisma peribadi.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk janji temu (date night) atau acara malam.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_CTA_005</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Miliki pesona maskulin malam ini.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>HPAS</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Generic Men Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_MEN_PERFUME_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_MEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Men Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Men's Perfume</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>men_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_ANG_006</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Sporty &amp; Fresh anti-odor</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_HOOK_006</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Sukan berpeluh tapi badan masih bau wangi. Ini rahsia jantan aktif.</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Teknologi kawalan bau badan aktif.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Wangian segar sitrus yang bertenaga sepanjang hari.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Tahan lasak dan tidak melarat apabila bercampur peluh.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>MEN_PERFUME_CTA_006</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Checkout untuk kesegaran aktif anda.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Generic Men Perfume row.</t>
         </is>
       </c>
     </row>
@@ -18699,7 +19883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -19005,6 +20189,786 @@
       <c r="AB2" s="5" t="inlineStr">
         <is>
           <t>Representative Fastmoss starter row. Generalize before large-scale Antigravity fill if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT_R002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Angin Herba Tradisional</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>TR_ANG_002</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>Stress &amp; Aroma Terapi</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>TR_HOOK_002</t>
+        </is>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>Dah lama tak rasa tenang? Satu sapu je, kepala terus sejuk.</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>Aroma herba semulajadi menyegarkan minda lesu.</t>
+        </is>
+      </c>
+      <c r="T3" s="7" t="inlineStr">
+        <is>
+          <t>Satu sapuan pantas rilekskan saraf tertekan.</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Formula aroma terapi warisan turun-temurun.</t>
+        </is>
+      </c>
+      <c r="V3" s="7" t="inlineStr">
+        <is>
+          <t>TR_CTA_002</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>Sapu rileks sekarang dan rasakan ketenangan.</t>
+        </is>
+      </c>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y3" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z3" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr">
+        <is>
+          <t>Generic direct remedy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT_R003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Angin Herba Tradisional</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>TR_ANG_003</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>Hidung Tersumbat &amp; Resdung</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>TR_HOOK_003</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>Hidung tersumbat dari pagi sampai malam? Cuba herba tradisi ni.</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>Bahan kayu putih membuka saluran pernafasan dengan pantas.</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>Sapuan luar tanpa perlu telan ubat.</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Melegakan hidung tersumbat terutamanya waktu sejuk.</t>
+        </is>
+      </c>
+      <c r="V4" s="7" t="inlineStr">
+        <is>
+          <t>TR_CTA_003</t>
+        </is>
+      </c>
+      <c r="W4" s="7" t="inlineStr">
+        <is>
+          <t>Sediakan satu botol di rumah untuk kecemasan.</t>
+        </is>
+      </c>
+      <c r="X4" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y4" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z4" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA4" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB4" s="7" t="inlineStr">
+        <is>
+          <t>Generic direct remedy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT_R004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Angin Herba Tradisional</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>TR_ANG_004</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Sakit Kepala &amp; Migrain</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>TR_HOOK_004</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Kepala berdenyut masa kerja? Sapu sikit kat pelipis terus rasa ringan.</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Haba dingin meresap melegakan denyutan kepala.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai digunakan semasa bekerja atau memandu.</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Reka bentuk botol compact mudah dibawa ke mana-mana.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>TR_CTA_004</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>Dapatkan kelegaan pantas sekarang.</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>Generic direct remedy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Angin Herba Tradisional</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>TR_ANG_005</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Sakit Sendi &amp; Lenguh Otot</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>TR_HOOK_005</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Sengal-sengal sendi lepas kerja berat? Urut 5 minit sebelum tidur.</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Melancarkan peredaran darah setempat.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Melegakan ketegangan otot di leher, bahu dan sendi.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk urutan seisi keluarga.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>TR_CTA_005</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Urut selesa hari ini sebelum tidur lena.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Generic direct remedy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Angin Herba Tradisional</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>TR_ANG_006</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Kembung Perut Bayi</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>TR_HOOK_006</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Bayi menangis malam sebab kembung perut? Sapu dan urut perlahan.</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Minyak lembut yang selamat untuk kulit bayi.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Mengeluarkan angin perut dengan pantas.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Formula herba semulajadi yang dipercayai generasi ibu.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>TR_CTA_006</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Klik beg kuning sekarang untuk standby.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Generic direct remedy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT_R007</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Angin Herba Tradisional</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>TR_ANG_007</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>Teman Travel Serbaguna</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>TR_HOOK_007</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>Satu botol kecil untuk 14 kegunaan harian masa travel.</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>Saiz travel-friendly mudah lepas pelepasan kastam.</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>Menyelesaikan masalah mual, pening, gatal digigit serangga.</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai diselipkan dalam beg tangan atau pouch.</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>TR_CTA_007</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>Sediakan payung sebelum hujan.</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y8" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z8" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA8" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB8" s="7" t="inlineStr">
+        <is>
+          <t>Generic direct remedy row.</t>
         </is>
       </c>
     </row>
@@ -19631,7 +21595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -20355,6 +22319,1110 @@
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>10ml flagship row seeded for direct Antigravity expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_BOSMAX_SERUM_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX_SERUM</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX Serum</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Sensitive stealth massage oil flagship</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>5 ml</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY lip balm size, fit into fingers naturally</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_01</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>ANG_002</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Performance confidence without obvious product signaling</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_002</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Piston lekat, bang. Ketuk sikit pun tak bunyi.</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Saiz lip balm ringkas, senang selit dalam poket jeans atau compartment kereta.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Kemasan botol hitam matte yang minimalis, tak nampak macam produk herba kelakian.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Formula herba pekat premium untuk sapuan pantas sebelum mula.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>CTA_002</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>OVERHAUL SEKARANG.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>SCRIPT_REGISTRY_UNIFIED.md + SCRIPT_VARIANT_LIBRARY.md + products/BOSMAX_SERUM.yaml</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing as of 2026-06-02.</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>5ml flagship row from male_health_vintage_car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_BOSMAX_SERUM_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX_SERUM</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX Serum</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Sensitive stealth massage oil flagship</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>5 ml</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY lip balm size, fit into fingers naturally</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_01</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>ANG_005</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Servis saluran utama</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_003</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Starter jam. Pulas kunci pun tak guna!</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Compact travel bottle muat selesa dalam genggaman tapak tangan.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Design roll-on memudahkan sapuan tanpa comotkan tangan atau membazir.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Packaging discreet tanpa sebarang visual lucah atau tulisan mengarut.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>CTA_003</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>ASAH SENJATA KAU.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>SCRIPT_REGISTRY_UNIFIED.md + SCRIPT_VARIANT_LIBRARY.md + products/BOSMAX_SERUM.yaml</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing as of 2026-06-02.</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>5ml flagship row from male_health_vintage_car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_BOSMAX_SERUM_R007</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX_SERUM</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX Serum</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Sensitive stealth massage oil flagship</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>5 ml</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY lip balm size, fit into fingers naturally</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_01</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>ANG_006</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>Malam Jumaat rescue</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_004</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>Malam Jumaat abang cari alasan? Sakit pinggang konon!</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>Saiz lip balm ringkas, bersedia bila-bila masa diperlukan.</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>Bahan herba natural gred tinggi tanpa kesan sampingan atau kebas terlampau.</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>Kemasan visual black-on-black maskulin dan nampak seperti barangan gaya hidup premium.</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>CTA_004</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>JANGAN CARI ALASAN.</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
+        <is>
+          <t>HPAS</t>
+        </is>
+      </c>
+      <c r="Y8" s="7" t="inlineStr">
+        <is>
+          <t>SCRIPT_REGISTRY_UNIFIED.md + SCRIPT_VARIANT_LIBRARY.md + products/BOSMAX_SERUM.yaml</t>
+        </is>
+      </c>
+      <c r="Z8" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing as of 2026-06-02.</t>
+        </is>
+      </c>
+      <c r="AA8" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB8" s="7" t="inlineStr">
+        <is>
+          <t>5ml flagship row from male_health_vintage_car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_BOSMAX_SERUM_R008</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX_SERUM</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX Serum</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Sensitive stealth massage oil flagship</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>10 ml</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY chapstick size, fit into fingers naturally</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_01</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>ANG_007</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>Naik taraf jentera</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_007</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>Luar nampak King. Dalam... enjin mati. Barang display!</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>Saiz chapstick 10ml, isipadu ganda dua untuk kegunaan lebih lama.</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>Label BOSMAX HERBS premium, sesuai diletakkan sebaris dengan penjagaan diri maskulin.</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>Semburan minyak aromatik lembut merangsang peredaran darah setempat.</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>CTA_007</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>KASI PADAT BALIK.</t>
+        </is>
+      </c>
+      <c r="X9" s="7" t="inlineStr">
+        <is>
+          <t>SAVAGE_HPAS</t>
+        </is>
+      </c>
+      <c r="Y9" s="7" t="inlineStr">
+        <is>
+          <t>SCRIPT_REGISTRY_UNIFIED.md + SCRIPT_VARIANT_LIBRARY.md + products/BOSMAX_SERUM.yaml</t>
+        </is>
+      </c>
+      <c r="Z9" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing as of 2026-06-02.</t>
+        </is>
+      </c>
+      <c r="AA9" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB9" s="7" t="inlineStr">
+        <is>
+          <t>10ml flagship row from male_health_vintage_car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_BOSMAX_SERUM_R009</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX_SERUM</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX Serum</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Sensitive stealth massage oil flagship</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>10 ml</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY chapstick size, fit into fingers naturally</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_01</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>ANG_008</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>Bateri kong rescue</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_008</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>Kunci dah pusing. Bateri kong terus. Sedih gaya abang!</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>Botol 10ml chapstick size yang selesa dipegang dan dibawa ke mana-mana.</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>Reka bentuk roll-on cap untuk aplikasi bersih dan tidak bocor.</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>Aroma herba maskulin yang tenang tanpa bau ubat tradisional yang menyengat.</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>CTA_008</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>JANGAN BLACKOUT.</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y10" s="7" t="inlineStr">
+        <is>
+          <t>SCRIPT_REGISTRY_UNIFIED.md + SCRIPT_VARIANT_LIBRARY.md + products/BOSMAX_SERUM.yaml</t>
+        </is>
+      </c>
+      <c r="Z10" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing as of 2026-06-02.</t>
+        </is>
+      </c>
+      <c r="AA10" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB10" s="7" t="inlineStr">
+        <is>
+          <t>10ml flagship row from male_health_vintage_car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_BOSMAX_SERUM_R010</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX_SERUM</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX Serum</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Sensitive stealth massage oil flagship</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>10 ml</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY chapstick size, fit into fingers naturally</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_01</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>ANG_009</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>Kuasa on-off jentera</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_009</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>Baru nak 'on'. Terus 'off'. Abang ni jentera rosak ke?</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>Saiz chapstick 10ml mudah disimpan dalam compartment laci atau poket baju.</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>Warna hitam monochrome nampak premium dan mengekalkan privasi abang.</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>Aplikasi sapuan licin dengan cooling sensation yang selesa.</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>CTA_009</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
+        <is>
+          <t>SERVIS SEKARANG.</t>
+        </is>
+      </c>
+      <c r="X11" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y11" s="7" t="inlineStr">
+        <is>
+          <t>SCRIPT_REGISTRY_UNIFIED.md + SCRIPT_VARIANT_LIBRARY.md + products/BOSMAX_SERUM.yaml</t>
+        </is>
+      </c>
+      <c r="Z11" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing as of 2026-06-02.</t>
+        </is>
+      </c>
+      <c r="AA11" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB11" s="7" t="inlineStr">
+        <is>
+          <t>10ml flagship row from male_health_vintage_car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_BOSMAX_SERUM_R011</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX_SERUM</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX Serum</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Sensitive stealth massage oil flagship</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>10 ml</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY chapstick size, fit into fingers naturally</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_01</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>ANG_010</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>Kuasa tersembunyi</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_010</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>Suasana romantis. Tapi abang blackout? Short-circuit lagi?</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>Isipadu 10ml lebih tahan lama dan sesuai untuk rutin urutan mingguan.</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>Formula minyak urut lelaki natural, melegakan otot dan melancarkan darah.</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>Label minimalis mengekalkan kerahsiaan penuh daripada pandangan tetamu.</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>CTA_010</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>JANGAN CARI ALASAN.</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>SCRIPT_REGISTRY_UNIFIED.md + SCRIPT_VARIANT_LIBRARY.md + products/BOSMAX_SERUM.yaml</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing as of 2026-06-02.</t>
+        </is>
+      </c>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB12" s="7" t="inlineStr">
+        <is>
+          <t>10ml flagship row from male_health_vintage_car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_BOSMAX_SERUM_R012</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX_SERUM</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>BOSMAX Serum</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Sensitive stealth massage oil flagship</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>10 ml</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY chapstick size, fit into fingers naturally</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_01</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>ANG_012</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>Tahan lasak</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_012</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>Bateri kong pagi-pagi. Abang ni jantan ke patung display?</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>Saiz chapstick 10ml, reka bentuk ergonomik untuk visual close-up.</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>Formula minyak urut lelaki natural, melegakan otot dan melancarkan darah.</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>Packaging sleek maskulin mengekalkan kehormatan dan maruah abang.</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>CTA_012</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>SERVIS SEKARANG.</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>SCRIPT_REGISTRY_UNIFIED.md + SCRIPT_VARIANT_LIBRARY.md + products/BOSMAX_SERUM.yaml</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing as of 2026-06-02.</t>
+        </is>
+      </c>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB13" s="7" t="inlineStr">
+        <is>
+          <t>10ml flagship row from male_health_vintage_car.</t>
         </is>
       </c>
     </row>
@@ -21977,7 +25045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22152,6 +25220,786 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL_R001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Urut Lelaki</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_generic</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_ANG_001</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>Enjin mati awal / stamina recovery</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_HOOK_001</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>Enjin panas terus mati. Kesian abang!</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>Saiz pocket-friendly, senang bawa tanpa menarik perhatian.</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>Kemasan premium discreet maskulin yang melindungi privasi.</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Formula herba premium untuk kelegaan otot tegang dan stamina.</t>
+        </is>
+      </c>
+      <c r="V2" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_CTA_001</t>
+        </is>
+      </c>
+      <c r="W2" s="7" t="inlineStr">
+        <is>
+          <t>SERVIS ENJIN KAU.</t>
+        </is>
+      </c>
+      <c r="X2" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y2" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z2" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB2" s="7" t="inlineStr">
+        <is>
+          <t>Generic stealth massage oil row using engine metaphor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL_R002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Urut Lelaki</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_generic</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_ANG_002</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>Starter jam / lancarkan peredaran</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_HOOK_002</t>
+        </is>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>Starter jam. Pulas kunci pun tak guna!</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>Compact travel bottle muat selesa dalam genggaman tapak tangan.</t>
+        </is>
+      </c>
+      <c r="T3" s="7" t="inlineStr">
+        <is>
+          <t>Design roll-on memudahkan sapuan tanpa comotkan tangan atau membazir.</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Packaging discreet tanpa sebarang visual lucah atau tulisan mengarut.</t>
+        </is>
+      </c>
+      <c r="V3" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_CTA_002</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>ASAH SENJATA KAU.</t>
+        </is>
+      </c>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y3" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z3" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr">
+        <is>
+          <t>Generic stealth massage oil row using engine metaphor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL_R003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Urut Lelaki</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_generic</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_ANG_003</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>Malam Jumaat rescue / stress relief</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_HOOK_003</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>Malam Jumaat abang cari alasan? Sakit pinggang konon!</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>Saiz lip balm ringkas, bersedia bila-bila masa diperlukan.</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>Bahan herba natural gred tinggi tanpa kesan sampingan atau kebas terlampau.</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Kemasan visual black-on-black maskulin dan nampak seperti barangan gaya hidup premium.</t>
+        </is>
+      </c>
+      <c r="V4" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_CTA_003</t>
+        </is>
+      </c>
+      <c r="W4" s="7" t="inlineStr">
+        <is>
+          <t>JANGAN CARI ALASAN.</t>
+        </is>
+      </c>
+      <c r="X4" s="7" t="inlineStr">
+        <is>
+          <t>HPAS</t>
+        </is>
+      </c>
+      <c r="Y4" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z4" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA4" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB4" s="7" t="inlineStr">
+        <is>
+          <t>Generic stealth massage oil row using engine metaphor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL_R004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Urut Lelaki</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_generic</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_ANG_004</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Naik taraf jentera / muscle building</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_HOOK_004</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Luar nampak King. Dalam... enjin mati. Barang display!</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Isipadu pocket-size yang selesa dipegang dan dibawa ke mana-mana.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Reka bentuk roll-on cap untuk aplikasi bersih dan tidak bocor.</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Aroma herba maskulin yang tenang tanpa bau ubat tradisional yang menyengat.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_CTA_004</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>KASI PADAT BALIK.</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>SAVAGE_HPAS</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>Generic stealth massage oil row using engine metaphor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Urut Lelaki</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_generic</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_ANG_005</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Bateri kong rescue / fatigue recovery</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_HOOK_005</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Kunci dah pusing. Bateri kong terus. Sedih gaya abang!</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Saiz mini travel muat selesa dalam compartment laci atau poket baju.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Warna hitam monochrome nampak premium dan mengekalkan privasi abang.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Aplikasi sapuan licin dengan cooling sensation yang selesa.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_CTA_005</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>JANGAN BLACKOUT.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Generic stealth massage oil row using engine metaphor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_STEALTH_MASSAGE_OIL</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Stealth Massage Oil</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Men's Health / Vitaliti Lelaki</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Urut Lelaki</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>male_health_stealth_generic</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_ANG_006</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Kuasa tersembunyi / performance restorer</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_HOOK_006</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Suasana romantis. Tapi abang blackout? Short-circuit lagi?</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Isipadu 10ml lebih tahan lama dan sesuai untuk rutin urutan mingguan.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Formula minyak urut lelaki natural, melegakan otot dan melancarkan darah.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Label minimalis mengekalkan kerahsiaan penuh daripada pandangan tetamu.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>STEALTH_CTA_006</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>JANGAN CARI ALASAN.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Generic stealth massage oil row using engine metaphor.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
   <dataValidations count="3">
@@ -22175,7 +26023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22350,6 +26198,786 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME_R001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Women Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Women's Perfume</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>women_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_ANG_001</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>Scent mood boost</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_HOOK_001</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>Hari bermula dengan bau manis yang bangkitkan mood positif.</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>Nota buah-buahan dan bunga-bungaan yang menyegarkan deria.</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>Memberikan rasa ceria dan bertenaga sepanjang pagi.</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk kegunaan harian dan melengkapkan penampilan.</t>
+        </is>
+      </c>
+      <c r="V2" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_CTA_001</t>
+        </is>
+      </c>
+      <c r="W2" s="7" t="inlineStr">
+        <is>
+          <t>Beli sekarang untuk hari yang ceria.</t>
+        </is>
+      </c>
+      <c r="X2" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y2" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z2" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB2" s="7" t="inlineStr">
+        <is>
+          <t>Generic Women Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME_R002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Women Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Women's Perfume</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>women_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_ANG_002</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>Date-night elegance</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_HOOK_002</t>
+        </is>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>Malam istimewa memerlukan wangian eksklusif yang buat dia tak lupa.</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>Nota bunga melur premium yang anggun dan feminin.</t>
+        </is>
+      </c>
+      <c r="T3" s="7" t="inlineStr">
+        <is>
+          <t>Wangian memikat yang bertahan sepanjang malam.</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Meningkatkan daya tarikan wanita sejati.</t>
+        </is>
+      </c>
+      <c r="V3" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_CTA_002</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>Miliki pesona anggun malam ini.</t>
+        </is>
+      </c>
+      <c r="X3" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y3" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z3" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr">
+        <is>
+          <t>Generic Women Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME_R003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Women Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Women's Perfume</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>women_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_ANG_003</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>All-day freshness</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_HOOK_003</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>Suhu panas di luar tapi badan kekal segar macam baru lepas mandi.</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>Aroma bersih menyegarkan sepanjang hari.</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>Formula anti-odor yang menghalang bau peluh.</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk wanita aktif di luar rumah.</t>
+        </is>
+      </c>
+      <c r="V4" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_CTA_003</t>
+        </is>
+      </c>
+      <c r="W4" s="7" t="inlineStr">
+        <is>
+          <t>Rasa kesegaran abadi sekarang.</t>
+        </is>
+      </c>
+      <c r="X4" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y4" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z4" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA4" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB4" s="7" t="inlineStr">
+        <is>
+          <t>Generic Women Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME_R004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Women Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Women's Perfume</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>women_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_ANG_004</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Luxury impression on a budget</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_HOOK_004</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Wangi mewah tak perlu habis beratus ringgit. Ini alternatif terbaik.</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Bahan berkualiti tinggi yang diinspirasikan daripada jenama mewah.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Harga mesra poket dengan hasil wangian eksklusif.</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Botol kaca yang cantik diletakkan di atas meja solek.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_CTA_004</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>Beli sekarang untuk tampil mewah.</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>HPAS</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>Generic Women Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Women Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Women's Perfume</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>women_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_ANG_005</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Compact travel spray</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_HOOK_005</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Botol mini senang bawa dalam bag mekap, touch-up bila-bila masa.</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Saiz travel-friendly mudah diselipkan dalam poket beg.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Penyembur halus rata tanpa meninggalkan kesan tompok pada baju.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk touch-up pantas sebelum mesyuarat atau keluar makan.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_CTA_005</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Dapatkan saiz poket anda sekarang.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Generic Women Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_WOMEN_PERFUME</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Women Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Women's Perfume</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>women_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_ANG_006</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Office workspace confidence</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_HOOK_006</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Rakan sekerja tegur bau wangi setiap kali lalu depan meja.</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Aroma tenang profesional yang tidak memeningkan kepala.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Wangian sederhana yang kekal melekat pada pakaian.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Membantu menonjolkan profesionalisme wanita bekerjaya.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>WOMEN_PERFUME_CTA_006</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Checkout di beg kuning hari ini.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>SAVAGE_HPAS</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Seed</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Generic Women Perfume row.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
   <dataValidations count="3">
@@ -22373,7 +27001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -23097,6 +27725,2214 @@
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>Freshness and calm direct row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Luka Kecil &amp; Surut Bengkak</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A05</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Jatuh lutut, lebam main futsal, kena piring panas — first aid box kau dah cukup ke?</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Haba minyak pecahkan tumpukan darah di bawah kulit — bengkak surut lebih laju</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Antiseptik semulajadi — bersihkan sekitar luka kecil, kurangkan risiko jangkitan</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Roll-on applicator — sentuh terus tanpa kotor tangan, hygienic untuk luka</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A05</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Letak kat first aid kit kau sekarang. Murah tapi kerja.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Sakit Gigi &amp; Bengkak Gusi</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A06</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Sakit gigi tengah malam. Klinik tutup. Ubat dah habis. Satu benda boleh tolong.</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Eugenol semulajadi dalam minyak herba — numbing agent tradisional untuk gusi dan gigi</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Roll tepi pipi luar dan urut perlahan — rasa sejuk masuk, sakit kurang dalam minit</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Bukan penawar kekal — tapi cukup untuk tahan malam tu dan pergi klinik esok pagi</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A06</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Simpan satu dalam laci ubat. Malam tak ada warning.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R007</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>Bayi Kembung Perut</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A07</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>Bayi nangis tak berhenti. Kembung? Ini yang mak-mak senior selalu guna.</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>Urut perlahan-lahan perut bayi dengan minyak — tekanan + haba longgarkan gas dalam usus</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>Formula tradisional — digunakan oleh generasi ibu Melayu selama 60+ tahun untuk bayi</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>Roll-on mudah — takde risiko terlampau banyak, aplikasi tepat dan terkawal</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A07</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>Letakkan dalam beg hospital sekarang. Guna dari hari pertama balik rumah.</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y8" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z8" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA8" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB8" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R008</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>Urutan Badan &amp; Saraf</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A08</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>Leher keras macam papan selepas kerja. 5 minit sebelum tidur, sapu dan urut. Esok pagi rasa beza.</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>Minyak meresap ke dalam lapisan otot — beri haba deep-relief untuk saraf yang tegang</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk urutan harian — bahu, leher, pinggang, lutut, tapak kaki</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>Lebih berkesan dengan urutan tekanan sederhana — aktifkan peredaran darah, kurangkan kekakuan</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A08</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>Satu botol untuk seluruh keluarga. Roll, urut, tidur lena.</t>
+        </is>
+      </c>
+      <c r="X9" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y9" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z9" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA9" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB9" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R009</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>Sakit Kepala &amp; Migrain</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A09</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>Kepala berdenyut masa meeting. Ubat panadol tak ada. Tapi poket selalu ada ini.</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>Roll kat pelipis kiri kanan + dahi — menthol dan herba sejukkan tekanan dalam kepala</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>Kerja dalam 2-3 minit — lebih laju dari tunggu panadol dissolve dalam perut</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>Boleh guna atas meja kerja — tak perlu air, tak perlu henti aktiviti</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A09</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>Masuk dalam drawer meja kerja sekarang. Sakit kepala tak tunggu masa sesuai.</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y10" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z10" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA10" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB10" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R010</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>Kembung Perut &amp; Senggugut (Haid)</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A10</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>Senggugut sampai baring atas lantai. Ada cara lebih cepat dari tunggu painkiller.</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>Roll dan urut perut bawah — haba minyak relakskan otot uterus yang berkontraksi</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>Bantu kempeskan angin dalam perut — kembung berkurang, badan rasa lebih ringan</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>Guna sebelum cramp teruk — preventive massage lebih efektif dari tunggu sakit dulu</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A10</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
+        <is>
+          <t>Simpan dalam almari ubat bilik. Bulan depan kau dah ready.</t>
+        </is>
+      </c>
+      <c r="X11" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y11" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z11" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA11" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB11" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R011</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>Mual &amp; Muntah / Mabuk Kenderaan</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A11</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>Mabuk bas. Nak muntah tapi malu. Sapu bawah hidung dulu.</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>Hidu aroma herba kuat — override signal mual dari otak, distract sistem saraf dari rasa nak muntah</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>Roll kat pergelangan tangan (titik P6) — teknik akupresur + aroma therapy gabungan</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>Selamat untuk ibu mengandung — tiada bahan larangan, guna dengan bimbingan doktor</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A11</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>Simpan dalam beg tangan. Jangan tunggu dah nak muntah baru cari.</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB12" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R012</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>Kencing Malam (Nocturia)</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A12</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>Bangun 3-4 kali malam nak kencing. Tidur tak cukup. Ada rawatan tradisional yang mungkin boleh bantu.</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>Lumur kawasan perut bawah dan ari-ari sebelum tidur — haba herba stimulate peredaran darah di kawasan pundi kencing</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>Cara rawatan tradisional Melayu yang diwarisi — bukan klaim perubatan, tapi amalan yang dipercayai</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>Tiada kesan sampingan — selamat untuk guna harian, konsisten adalah kunci</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A12</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>Cuba 2 minggu konsisten. Roll sebelum tidur tiap malam.</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB13" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R013</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>Urutan Sebelum &amp; Selepas Bersalin</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A13</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>Badan lenguh-lenguh masa mengandung. Badan sakit-sakit selepas bersalin. Ini yang mak-mak pakai.</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>Melegakan sakit otot dan sendi yang terbeban semasa mengandung — selamat untuk trimester 3</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>Selepas bersalin — urutan dengan minyak Cap Burung bantu keluarkan angin, relakskan otot yang tertekan masa bersalin</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>Boleh digunakan oleh bidan dan orang tua semasa urutan tradisional — formula dipercayai</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A13</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>Masuk dalam hospital bag kau. Guna dari hari pertama.</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB14" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R014</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>Param &amp; Bengkung Postnatal</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A14</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>Nak kempiskan perut selepas bersalin? Minyak param adalah asas yang selalu dilupa.</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>Membantu mengecutkan rahim — haba minyak tembus bantu proses involution uterus semulajadi</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr">
+        <is>
+          <t>Wajib guna sebelum bengkung — minyak jadikan kulit lebih reseptif, bengkung lebih berkesan</t>
+        </is>
+      </c>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>Digunakan dalam rawatan param tradisional Melayu — formula yang bidan kenal dan amalkan</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A14</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>Order sebelum due date. Wajib dalam kit pantang kau.</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB15" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R015</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>Travel Essential / Simpanan Poket</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A15</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>Satu botol kecil. 14 kegunaan. Bawak dalam beg dah settle separuh masalah perjalanan.</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>Saiz travel-friendly — 30ML, muat dalam poket seluar, beg tangan, pouch haji</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>Cover semua emergency asas: sakit kepala, mabuk, kembung, gigitan, luka kecil</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>Tiada had liquid untuk penerbangan domestik — bawak naik kapal terbang tanpa masalah</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A15</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>Satu untuk rumah, satu untuk beg travel. Jangan keluar rumah tanpa.</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB16" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R016</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>Warisan 1958 / Heritage Trust</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A16</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>Arwah nenek kau simpan ni dalam laci dia. Mak kau pun ada. Sekarang giliran kau.</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>Sejak 1958 — bukan trend baru, bukan viral seminggu. 60+ tahun ia berkesan untuk keluarga Melayu</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>Formula turun-temurun — bukan diubah ikut trend, tapi dikekalkan sebab ia memang kerja</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>Kepercayaan yang tak boleh dibeli dengan iklan — ia dibina satu generasi ke satu generasi</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A16</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>Beli untuk kau. Beli untuk mak. Teruskan tradisi keluarga.</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB17" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R017</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Fungsi / Value Proposition</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A17</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>Kalau nak beli ubat sakit kepala, ubat kembung, ubat gatal, ubat mual berasingan — berapa dah habis? Ini satu untuk semua.</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>14 kegunaan dalam satu botol 30ML — jimat ruang, jimat duit, jimat masa</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>Ganti 5-6 jenis ubat luar yang selalu habis — satu restock, semua covered</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>Harga unit rendah berbanding nilai yang diberi — ROI tertinggi dalam first aid kit kau</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A17</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>Kira balik berapa kau belanja ubat-ubatan sebulan. Lepas tu tengok harga ni.</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB18" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R018</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>Postnatal Recovery Comprehensive</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A18</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>Selepas bersalin, badan macam dah perang. Ini cara mak-mak zaman dulu recover tanpa 10 jenis supplement.</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>3 in 1 untuk postnatal: urutan badan + param perut + bengkung — semua guna Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>Selamat untuk ibu menyusu — formula herba semulajadi tanpa bahan sintetik berbahaya</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>Jimat kos pantang — satu botol cover urutan harian selama tempoh pantang penuh</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A18</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>Masuk dalam wishlist pantang kau sekarang. Share dengan mak dan ibu mertua.</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB19" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R019</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>Baby &amp; Kids Care</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A19</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>Kau nak sapu produk apa kat anak kau yang tak tau bahan-bahannya? Ini nenek kau dah guna 60 tahun.</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>Formula tradisional yang generasi demi generasi guna untuk kanak-kanak — rekod keselamatan 60+ tahun</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
+        <is>
+          <t>Cover kegunaan biasa untuk kanak-kanak: selesema, kembung, gatal gigitan, lelah</t>
+        </is>
+      </c>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>Orang tua dan mak mertua confirm faham — tak payah argue pasal produk apa nak guna</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A19</t>
+        </is>
+      </c>
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>Tanya mak kau dulu. Lepas tu order satu untuk rumah kau sendiri.</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB20" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCT_MW_CAP_BURUNG_R020</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_TRADITIONAL_REMEDY_DIRECT</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy Direct</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>CAP_BURUNG_MINYAK</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Minyak Warisan Cap Burung</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Remedy / Minyak Urut</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Traditional Malay herbal liniment / minyak angin in WG40 glass bottle</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Bottle</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>30 ml</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>EXACTLY a small pocket-size 30ml rectangular clear glass medicated oil bottle with a red ribbed cap, shorter than the palm and only two fingers wide</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>traditional_remedy_direct</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>Wanita Aktif / Busy Mom</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>HOOK_A20</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>Masak, kerja, jaga anak, jaga mak — badan kau penat tapi kau tak boleh berhenti. Setidaknya ada yang boleh bantu.</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>Cover 5 masalah biasa wanita aktif: stres, sakit kepala, senggugut, kembung, badan lenguh</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>Guna dalam masa 30 saat — tak perlu henti kerja, tak perlu minum ubat, terus sambung</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Muat dalam handbag — sentiasa ada bila diperlukan, tak perlu storage besar</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>CTA_A20</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>Satu untuk dalam handbag. Satu untuk laci meja kerja. Jangan kehabisan.</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>products/CAP_BURUNG_MINYAK.yaml</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
+        <is>
+          <t>No confirmed direct Fastmoss listing mapped yet; use product registry truth first.</t>
+        </is>
+      </c>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB21" s="7" t="inlineStr">
+        <is>
+          <t>Imported from products/CAP_BURUNG_MINYAK.yaml copywriting_angles.</t>
         </is>
       </c>
     </row>
@@ -24323,7 +31159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -24900,6 +31736,396 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_UNISEX_PERFUME_R004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_UNISEX_PERFUME</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Unisex Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Unisex Perfume</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>unisex_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_ANG_004</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Everyday versatility</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_HOOK_004</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Wangian neutral yang sesuai untuk lelaki mahupun wanita, tak pening kepala pilih.</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Nota kayu dan sitrus neutral sesuai untuk kedua-dua jantina.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai dikongsi bersama pasangan untuk menjimatkan belanja.</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Bau serbaguna yang sesuai untuk sebarang acara.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_CTA_004</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>Beli satu untuk berkongsi kesegaran hari ini.</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>Generic Unisex Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_UNISEX_PERFUME_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_UNISEX_PERFUME</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Unisex Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Unisex Perfume</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>unisex_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_ANG_005</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Premium hotel clean vibe</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_HOOK_005</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Bau bersih menyegarkan seperti baru keluar dari lobi hotel mewah.</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Aroma linen segar dan lavender yang menenangkan.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Memberikan impresi kemas, bersih dan teratur.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Bau mesra persekitaran yang digemari ramai.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_CTA_005</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Dapatkan vibe bersih segar anda sekarang.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Generic Unisex Perfume row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_UNISEX_PERFUME_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_UNISEX_PERFUME</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Unisex Perfume Direct</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Unisex Perfume</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>unisex_perfume_direct</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_ANG_006</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Travel convenience</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_HOOK_006</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Satu botol kecil yang memenuhi semua keperluan wangian percutian anda.</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Memenuhi syarat pelepasan cecair lapangan terbang.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Wangian neutral pelbagai guna untuk siang dan malam.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Packaging kukuh dan kalis bocor sesuai dalam beg.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>UNISEX_PERFUME_CTA_006</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Add to cart sebelum percutian anda bermula.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Generic Unisex Perfume row.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AB4"/>
   <dataValidations count="3">
@@ -24923,7 +32149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -25500,6 +32726,396 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_FASHION_STYLE_FIT_R004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_FASHION_STYLE_FIT</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Fashion Style Fit Direct</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Apparel / Modest Fashion</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Menswear / Womenswear</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Clothing Modest / Sportswear</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>fashion_style_fit_direct</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_ANG_004</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Modern modest fit &amp; instant shape</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_HOOK_004</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Hijab segera yang terbentuk kemas di muka dalam masa 10 saat saja.</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Material awning anti-kedut tahan kemek sepanjang hari.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Potongan selesa menutupi dada dengan labuh ideal.</t>
+        </is>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Sesuai untuk wanita bekerja yang sentiasa sibuk.</t>
+        </is>
+      </c>
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_CTA_004</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>Pilih warna kegemaran anda sekarang.</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>AIDA</t>
+        </is>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB5" s="7" t="inlineStr">
+        <is>
+          <t>Generic Fashion Style Fit row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_FASHION_STYLE_FIT_R005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_FASHION_STYLE_FIT</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Fashion Style Fit Direct</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Apparel / Modest Fashion</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Menswear / Womenswear</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Clothing Modest / Sportswear</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>fashion_style_fit_direct</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_ANG_005</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Non-iron travel shirts</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_HOOK_005</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>Baju kemeja yang tak perlu gosok, sesuai untuk travel dan terus sarung.</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>Fabrik premium anti-kedut gred tinggi.</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>Material sejuk bernafas selesa di bawah cuaca panas.</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>Potongan fit moden kelihatan kemas tanpa gosokan keras.</t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_CTA_005</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Beli sekarang untuk travel tanpa stress.</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
+        <is>
+          <t>HSO</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB6" s="7" t="inlineStr">
+        <is>
+          <t>Generic Fashion Style Fit row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_FASHION_STYLE_FIT_R006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ARCH_FASHION_STYLE_FIT</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Fashion Style Fit Direct</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Apparel / Modest Fashion</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Menswear / Womenswear</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Clothing Modest / Sportswear</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>VARIES_BY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>SEE_PRODUCT_TRUTH</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>fashion_style_fit_direct</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_ANG_006</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Sportswear stretch durability</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_HOOK_006</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>Seluar sukan yang memeri dan selesa untuk semua aktiviti kecergasan.</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Fabrik stretch 4-hala yang tahan lasak.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Material penyerap peluh cepat kering (dry-fit).</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Pinggang elastik dengan tali pengikat selesa.</t>
+        </is>
+      </c>
+      <c r="V7" s="7" t="inlineStr">
+        <is>
+          <t>FASHION_CTA_006</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>Dapatkan saiz anda sekarang.</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Archetype Library Expansion</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Generic library row</t>
+        </is>
+      </c>
+      <c r="AA7" s="7" t="inlineStr">
+        <is>
+          <t>SEED_READY</t>
+        </is>
+      </c>
+      <c r="AB7" s="7" t="inlineStr">
+        <is>
+          <t>Generic Fashion Style Fit row.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AB4"/>
   <dataValidations count="3">
